--- a/planilha_teste.xlsx
+++ b/planilha_teste.xlsx
@@ -436,7 +436,7 @@
         <v>123.456.789-00</v>
       </c>
       <c r="C2" t="str">
-        <v>5521966491519</v>
+        <v>5521981811077</v>
       </c>
       <c r="D2" t="str">
         <v>189,90</v>
